--- a/recoverability.xlsx
+++ b/recoverability.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\YuKi_Project\R_Packages\RL\RLWMH\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ED9D4348-7736-4731-AC0F-734BB6C70CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8F00B33-BF1C-40C7-909C-05E50C227E36}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11364" yWindow="1248" windowWidth="19320" windowHeight="14352" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14256" yWindow="1512" windowWidth="25776" windowHeight="14352" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,122 +25,110 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="289" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="282" uniqueCount="41">
   <si>
     <t>TD</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>beta</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>gamma</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>delta</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>epsilon</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>zeta</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>weight</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>capacity</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>TD(decay)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>free</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>NA</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Q0</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>reset</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>WM</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>WM(bonus)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>alpha(RL)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>alpha(WM)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>sticky</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>lapse</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>WMH</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RSWM</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RLWM</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>free/free</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>H</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>H(decay)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>MLE</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>ABC</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RNN</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>Estimator</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RLWM(-weight)</t>
@@ -153,7 +141,7 @@
   </si>
   <si>
     <t>FAIL</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>HWM(-weight)</t>
@@ -166,28 +154,53 @@
   </si>
   <si>
     <t>HWM</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>HWM(+lapse)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>RLWM(+lapse)</t>
-    <phoneticPr fontId="7" type="noConversion"/>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>RLWM(+sticky)</t>
+  </si>
+  <si>
+    <t>HWM(+sticky)</t>
+  </si>
+  <si>
+    <t>0.02/0.03</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.05/0.23</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>0.20/0.20</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="10">
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -250,6 +263,14 @@
     <font>
       <sz val="12"/>
       <color theme="0"/>
+      <name val="Times New Roman"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF00B050"/>
       <name val="Times New Roman"/>
       <family val="2"/>
       <charset val="134"/>
@@ -378,64 +399,70 @@
   </borders>
   <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="4" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" xfId="4" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="3" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="3" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="3" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="4" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="3" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="9" borderId="1" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" xfId="3" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="10" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="3" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -722,7 +749,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O63"/>
+  <dimension ref="A1:O69"/>
   <sheetFormatPr defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="1" width="21.109375" bestFit="1" customWidth="1"/>
@@ -734,13 +761,13 @@
     <row r="1" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A1" s="2"/>
       <c r="B1" s="2" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>15</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>16</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>1</v>
@@ -764,16 +791,16 @@
         <v>7</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
       <c r="N1" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="O1" s="8" t="s">
         <v>17</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
@@ -781,13 +808,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C2" s="10">
         <v>0.89</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E2" s="3">
         <v>25</v>
@@ -799,16 +826,16 @@
         <v>0</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I2" s="3">
         <v>0</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L2" s="1">
         <v>0.33</v>
@@ -828,13 +855,13 @@
         <v>0</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C3" s="14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E3" s="3">
         <v>25</v>
@@ -846,16 +873,16 @@
         <v>0</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I3" s="3">
         <v>0</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K3" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L3" s="1">
         <v>0.33</v>
@@ -875,13 +902,13 @@
         <v>0</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C4" s="10">
         <v>0.96</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" s="3">
         <v>25</v>
@@ -893,16 +920,16 @@
         <v>0</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I4" s="3">
         <v>0</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L4" s="1">
         <v>0.33</v>
@@ -922,13 +949,13 @@
         <v>8</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C5" s="10">
         <v>0.75</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E5" s="3">
         <v>25</v>
@@ -940,16 +967,16 @@
         <v>0</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I5" s="10">
         <v>0.93</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L5" s="1">
         <v>0.33</v>
@@ -969,13 +996,13 @@
         <v>8</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C6" s="10">
         <v>0.98</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E6" s="3">
         <v>25</v>
@@ -987,16 +1014,16 @@
         <v>0</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I6" s="10">
         <v>0.99</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L6" s="1">
         <v>0.33</v>
@@ -1016,13 +1043,13 @@
         <v>8</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C7" s="10">
         <v>0.96</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E7" s="3">
         <v>25</v>
@@ -1034,16 +1061,16 @@
         <v>0</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I7" s="10">
         <v>0.98</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L7" s="1">
         <v>0.33</v>
@@ -1060,16 +1087,16 @@
     </row>
     <row r="8" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A8" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C8" s="10">
         <v>0.89</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E8" s="3">
         <v>25</v>
@@ -1081,16 +1108,16 @@
         <v>0</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I8" s="3">
         <v>0</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L8" s="1">
         <v>0.33</v>
@@ -1107,16 +1134,16 @@
     </row>
     <row r="9" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>26</v>
-      </c>
       <c r="C9" s="14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E9" s="3">
         <v>25</v>
@@ -1128,16 +1155,16 @@
         <v>0</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I9" s="3">
         <v>0</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L9" s="1">
         <v>0.33</v>
@@ -1154,16 +1181,16 @@
     </row>
     <row r="10" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A10" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B10" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C10" s="10">
         <v>0.96</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E10" s="3">
         <v>25</v>
@@ -1175,16 +1202,16 @@
         <v>0</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I10" s="3">
         <v>0</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L10" s="1">
         <v>0.33</v>
@@ -1201,16 +1228,16 @@
     </row>
     <row r="11" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A11" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C11" s="10">
         <v>0.75</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E11" s="3">
         <v>25</v>
@@ -1222,16 +1249,16 @@
         <v>0</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I11" s="10">
         <v>0.93</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L11" s="1">
         <v>0.33</v>
@@ -1248,16 +1275,16 @@
     </row>
     <row r="12" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A12" s="2" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="B12" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C12" s="10">
         <v>0.98</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E12" s="3">
         <v>25</v>
@@ -1269,16 +1296,16 @@
         <v>0</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I12" s="10">
         <v>0.99</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L12" s="1">
         <v>0.33</v>
@@ -1295,16 +1322,16 @@
     </row>
     <row r="13" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A13" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B13" s="13" t="s">
         <v>24</v>
-      </c>
-      <c r="B13" s="13" t="s">
-        <v>27</v>
       </c>
       <c r="C13" s="10">
         <v>0.88</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E13" s="3">
         <v>25</v>
@@ -1316,16 +1343,16 @@
         <v>0</v>
       </c>
       <c r="H13" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I13" s="10">
         <v>0.97</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L13" s="1">
         <v>0.33</v>
@@ -1342,13 +1369,13 @@
     </row>
     <row r="14" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A14" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D14" s="3">
         <v>1</v>
@@ -1363,16 +1390,16 @@
         <v>0</v>
       </c>
       <c r="H14" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I14" s="10">
         <v>0.87</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L14" s="1">
         <v>0.33</v>
@@ -1389,13 +1416,13 @@
     </row>
     <row r="15" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A15" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D15" s="3">
         <v>1</v>
@@ -1410,16 +1437,16 @@
         <v>0</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I15" s="10">
         <v>0.99</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L15" s="1">
         <v>0.33</v>
@@ -1436,13 +1463,13 @@
     </row>
     <row r="16" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A16" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B16" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D16" s="3">
         <v>1</v>
@@ -1457,16 +1484,16 @@
         <v>0</v>
       </c>
       <c r="H16" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I16" s="10">
         <v>0.99</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L16" s="1">
         <v>0.33</v>
@@ -1483,13 +1510,13 @@
     </row>
     <row r="17" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A17" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D17" s="3">
         <v>1</v>
@@ -1504,16 +1531,16 @@
         <v>0</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I17" s="10">
         <v>0.96</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L17" s="1">
         <v>0.33</v>
@@ -1530,13 +1557,13 @@
     </row>
     <row r="18" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A18" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D18" s="3">
         <v>1</v>
@@ -1551,16 +1578,16 @@
         <v>0</v>
       </c>
       <c r="H18" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I18" s="10">
         <v>0.99</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L18" s="1">
         <v>0.33</v>
@@ -1577,13 +1604,13 @@
     </row>
     <row r="19" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A19" s="2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D19" s="3">
         <v>1</v>
@@ -1598,16 +1625,16 @@
         <v>0</v>
       </c>
       <c r="H19" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I19" s="10">
         <v>0.99</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L19" s="1">
         <v>0.33</v>
@@ -1641,10 +1668,10 @@
     </row>
     <row r="21" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A21" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B21" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C21" s="10">
         <v>0.32</v>
@@ -1662,7 +1689,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I21" s="10">
         <v>0.55000000000000004</v>
@@ -1687,11 +1714,11 @@
       </c>
     </row>
     <row r="22" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
-      <c r="A22" s="2" t="s">
-        <v>21</v>
+      <c r="A22" s="17" t="s">
+        <v>19</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C22" s="10">
         <v>0.65</v>
@@ -1709,7 +1736,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I22" s="10">
         <v>0.98</v>
@@ -1735,10 +1762,10 @@
     </row>
     <row r="23" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A23" s="2" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B23" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C23" s="10">
         <v>0.28999999999999998</v>
@@ -1756,7 +1783,7 @@
         <v>0</v>
       </c>
       <c r="H23" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I23" s="10">
         <v>0.98</v>
@@ -1782,10 +1809,10 @@
     </row>
     <row r="24" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A24" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C24" s="10">
         <v>-0.01</v>
@@ -1803,13 +1830,13 @@
         <v>0</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I24" s="10">
         <v>0.99</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K24" s="10">
         <v>0.86</v>
@@ -1828,11 +1855,11 @@
       </c>
     </row>
     <row r="25" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
-      <c r="A25" s="2" t="s">
-        <v>29</v>
+      <c r="A25" s="17" t="s">
+        <v>26</v>
       </c>
       <c r="B25" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C25" s="10">
         <v>0.75</v>
@@ -1850,13 +1877,13 @@
         <v>0</v>
       </c>
       <c r="H25" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I25" s="10">
         <v>0.99</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K25" s="10">
         <v>0.98</v>
@@ -1876,10 +1903,10 @@
     </row>
     <row r="26" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A26" s="2" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B26" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C26" s="10">
         <v>0.17</v>
@@ -1897,13 +1924,13 @@
         <v>0</v>
       </c>
       <c r="H26" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I26" s="10">
         <v>0.99</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K26" s="10">
         <v>0.93</v>
@@ -1923,10 +1950,10 @@
     </row>
     <row r="27" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A27" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B27" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C27" s="10">
         <v>0.87</v>
@@ -1944,7 +1971,7 @@
         <v>0</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I27" s="3">
         <v>0</v>
@@ -1970,13 +1997,13 @@
     </row>
     <row r="28" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A28" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B28" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C28" s="14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D28" s="3">
         <v>1</v>
@@ -1991,16 +2018,16 @@
         <v>0</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I28" s="3">
         <v>0</v>
       </c>
       <c r="J28" s="14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="K28" s="14" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="L28" s="1">
         <v>0.33</v>
@@ -2017,10 +2044,10 @@
     </row>
     <row r="29" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A29" s="2" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B29" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C29" s="10">
         <v>0.89</v>
@@ -2038,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="H29" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -2064,10 +2091,10 @@
     </row>
     <row r="30" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A30" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B30" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C30" s="10">
         <v>0.18</v>
@@ -2085,7 +2112,7 @@
         <v>0</v>
       </c>
       <c r="H30" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I30" s="10">
         <v>0.92</v>
@@ -2094,7 +2121,7 @@
         <v>0.69</v>
       </c>
       <c r="K30" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L30" s="1">
         <v>0.33</v>
@@ -2110,11 +2137,11 @@
       </c>
     </row>
     <row r="31" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
-      <c r="A31" s="2" t="s">
-        <v>31</v>
+      <c r="A31" s="17" t="s">
+        <v>28</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C31" s="10">
         <v>0.85</v>
@@ -2132,7 +2159,7 @@
         <v>0</v>
       </c>
       <c r="H31" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I31" s="10">
         <v>0.99</v>
@@ -2141,7 +2168,7 @@
         <v>0.99</v>
       </c>
       <c r="K31" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L31" s="1">
         <v>0.33</v>
@@ -2158,10 +2185,10 @@
     </row>
     <row r="32" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A32" s="2" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="B32" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C32" s="10">
         <v>0.6</v>
@@ -2179,7 +2206,7 @@
         <v>0</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I32" s="10">
         <v>0.99</v>
@@ -2188,7 +2215,7 @@
         <v>0.93</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L32" s="1">
         <v>0.33</v>
@@ -2222,10 +2249,10 @@
     </row>
     <row r="34" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A34" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B34" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C34" s="10">
         <v>0.44</v>
@@ -2243,7 +2270,7 @@
         <v>0</v>
       </c>
       <c r="H34" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I34" s="10">
         <v>0.27</v>
@@ -2268,11 +2295,11 @@
       </c>
     </row>
     <row r="35" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
-      <c r="A35" s="2" t="s">
-        <v>36</v>
+      <c r="A35" s="17" t="s">
+        <v>33</v>
       </c>
       <c r="B35" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C35" s="10">
         <v>0.55000000000000004</v>
@@ -2290,7 +2317,7 @@
         <v>0</v>
       </c>
       <c r="H35" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I35" s="10">
         <v>0.9</v>
@@ -2316,10 +2343,10 @@
     </row>
     <row r="36" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A36" s="2" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B36" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C36" s="10">
         <v>0.61</v>
@@ -2337,7 +2364,7 @@
         <v>0</v>
       </c>
       <c r="H36" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I36" s="10">
         <v>0.95</v>
@@ -2363,10 +2390,10 @@
     </row>
     <row r="37" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A37" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B37" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C37" s="10">
         <v>0.38</v>
@@ -2384,13 +2411,13 @@
         <v>0</v>
       </c>
       <c r="H37" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I37" s="10">
         <v>0.96</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K37" s="10">
         <v>0.89</v>
@@ -2409,11 +2436,11 @@
       </c>
     </row>
     <row r="38" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
-      <c r="A38" s="2" t="s">
-        <v>33</v>
+      <c r="A38" s="17" t="s">
+        <v>30</v>
       </c>
       <c r="B38" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C38" s="10">
         <v>0.76</v>
@@ -2431,13 +2458,13 @@
         <v>0</v>
       </c>
       <c r="H38" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I38" s="10">
         <v>0.99</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K38" s="10">
         <v>0.99</v>
@@ -2457,10 +2484,10 @@
     </row>
     <row r="39" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A39" s="2" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B39" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C39" s="10">
         <v>0.31</v>
@@ -2478,13 +2505,13 @@
         <v>0</v>
       </c>
       <c r="H39" s="4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I39" s="10">
         <v>0.99</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="K39" s="10">
         <v>0.99</v>
@@ -2504,10 +2531,10 @@
     </row>
     <row r="40" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A40" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C40" s="10">
         <v>0.2</v>
@@ -2525,7 +2552,7 @@
         <v>0</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I40" s="3">
         <v>0</v>
@@ -2550,11 +2577,11 @@
       </c>
     </row>
     <row r="41" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
-      <c r="A41" s="2" t="s">
-        <v>34</v>
+      <c r="A41" s="17" t="s">
+        <v>31</v>
       </c>
       <c r="B41" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C41" s="10">
         <v>0.91</v>
@@ -2572,7 +2599,7 @@
         <v>0</v>
       </c>
       <c r="H41" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I41" s="3">
         <v>0</v>
@@ -2598,10 +2625,10 @@
     </row>
     <row r="42" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A42" s="2" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="B42" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C42" s="10">
         <v>0.6</v>
@@ -2619,7 +2646,7 @@
         <v>0</v>
       </c>
       <c r="H42" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I42" s="3">
         <v>0</v>
@@ -2645,10 +2672,10 @@
     </row>
     <row r="43" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A43" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B43" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C43" s="10">
         <v>0.25</v>
@@ -2666,7 +2693,7 @@
         <v>0</v>
       </c>
       <c r="H43" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I43" s="10">
         <v>0.89</v>
@@ -2675,7 +2702,7 @@
         <v>0.99</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L43" s="1">
         <v>0.33</v>
@@ -2691,11 +2718,11 @@
       </c>
     </row>
     <row r="44" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
-      <c r="A44" s="2" t="s">
-        <v>35</v>
+      <c r="A44" s="17" t="s">
+        <v>32</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C44" s="10">
         <v>0.81</v>
@@ -2713,7 +2740,7 @@
         <v>0</v>
       </c>
       <c r="H44" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I44" s="10">
         <v>0.98</v>
@@ -2722,7 +2749,7 @@
         <v>0.99</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L44" s="1">
         <v>0.33</v>
@@ -2739,10 +2766,10 @@
     </row>
     <row r="45" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A45" s="2" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B45" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C45" s="10">
         <v>0.63</v>
@@ -2760,7 +2787,7 @@
         <v>0</v>
       </c>
       <c r="H45" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I45" s="10">
         <v>0.98</v>
@@ -2769,7 +2796,7 @@
         <v>0.99</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L45" s="1">
         <v>0.33</v>
@@ -2803,12 +2830,14 @@
     </row>
     <row r="47" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A47" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B47" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C47" s="10"/>
+        <v>22</v>
+      </c>
+      <c r="C47" s="10">
+        <v>0.26</v>
+      </c>
       <c r="D47" s="3">
         <v>1</v>
       </c>
@@ -2822,11 +2851,17 @@
         <v>0</v>
       </c>
       <c r="H47" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I47" s="10"/>
-      <c r="J47" s="10"/>
-      <c r="K47" s="10"/>
+        <v>9</v>
+      </c>
+      <c r="I47" s="10">
+        <v>0.19</v>
+      </c>
+      <c r="J47" s="10">
+        <v>0.2</v>
+      </c>
+      <c r="K47" s="10">
+        <v>0.01</v>
+      </c>
       <c r="L47" s="1">
         <v>0.33</v>
       </c>
@@ -2836,16 +2871,20 @@
       <c r="N47" s="9">
         <v>0</v>
       </c>
-      <c r="O47" s="10"/>
+      <c r="O47" s="10">
+        <v>-0.01</v>
+      </c>
     </row>
     <row r="48" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A48" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B48" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C48" s="10"/>
+        <v>23</v>
+      </c>
+      <c r="C48" s="10">
+        <v>0.41</v>
+      </c>
       <c r="D48" s="3">
         <v>1</v>
       </c>
@@ -2859,11 +2898,17 @@
         <v>0</v>
       </c>
       <c r="H48" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I48" s="10"/>
-      <c r="J48" s="10"/>
-      <c r="K48" s="10"/>
+        <v>9</v>
+      </c>
+      <c r="I48" s="10">
+        <v>0.86</v>
+      </c>
+      <c r="J48" s="10">
+        <v>0.53</v>
+      </c>
+      <c r="K48" s="10">
+        <v>0.34</v>
+      </c>
       <c r="L48" s="1">
         <v>0.33</v>
       </c>
@@ -2873,16 +2918,20 @@
       <c r="N48" s="9">
         <v>0</v>
       </c>
-      <c r="O48" s="10"/>
+      <c r="O48" s="10">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="49" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A49" s="2" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="B49" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C49" s="10"/>
+        <v>24</v>
+      </c>
+      <c r="C49" s="10">
+        <v>0.04</v>
+      </c>
       <c r="D49" s="3">
         <v>1</v>
       </c>
@@ -2896,11 +2945,17 @@
         <v>0</v>
       </c>
       <c r="H49" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I49" s="10"/>
-      <c r="J49" s="10"/>
-      <c r="K49" s="10"/>
+        <v>9</v>
+      </c>
+      <c r="I49" s="10">
+        <v>0.67</v>
+      </c>
+      <c r="J49" s="10">
+        <v>0.45</v>
+      </c>
+      <c r="K49" s="10">
+        <v>0.1</v>
+      </c>
       <c r="L49" s="1">
         <v>0.33</v>
       </c>
@@ -2910,16 +2965,20 @@
       <c r="N49" s="9">
         <v>0</v>
       </c>
-      <c r="O49" s="10"/>
+      <c r="O49" s="10">
+        <v>0.99</v>
+      </c>
     </row>
     <row r="50" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A50" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B50" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C50" s="10"/>
+        <v>22</v>
+      </c>
+      <c r="C50" s="10">
+        <v>0.4</v>
+      </c>
       <c r="D50" s="3">
         <v>1</v>
       </c>
@@ -2933,11 +2992,17 @@
         <v>0</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I50" s="10"/>
-      <c r="J50" s="10"/>
-      <c r="K50" s="10"/>
+        <v>9</v>
+      </c>
+      <c r="I50" s="10">
+        <v>0.27</v>
+      </c>
+      <c r="J50" s="10">
+        <v>0.44</v>
+      </c>
+      <c r="K50" s="10">
+        <v>0.27</v>
+      </c>
       <c r="L50" s="1">
         <v>0.33</v>
       </c>
@@ -2947,16 +3012,20 @@
       <c r="N50" s="9">
         <v>0</v>
       </c>
-      <c r="O50" s="10"/>
+      <c r="O50" s="10">
+        <v>0.23</v>
+      </c>
     </row>
     <row r="51" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
-      <c r="A51" s="2" t="s">
-        <v>37</v>
+      <c r="A51" s="17" t="s">
+        <v>34</v>
       </c>
       <c r="B51" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C51" s="10"/>
+        <v>23</v>
+      </c>
+      <c r="C51" s="10">
+        <v>0.68</v>
+      </c>
       <c r="D51" s="3">
         <v>1</v>
       </c>
@@ -2970,11 +3039,17 @@
         <v>0</v>
       </c>
       <c r="H51" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
-      <c r="K51" s="10"/>
+        <v>9</v>
+      </c>
+      <c r="I51" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="J51" s="10">
+        <v>0.92</v>
+      </c>
+      <c r="K51" s="10">
+        <v>0.67</v>
+      </c>
       <c r="L51" s="1">
         <v>0.33</v>
       </c>
@@ -2984,16 +3059,20 @@
       <c r="N51" s="9">
         <v>0</v>
       </c>
-      <c r="O51" s="10"/>
+      <c r="O51" s="10">
+        <v>0.97</v>
+      </c>
     </row>
     <row r="52" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A52" s="2" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B52" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C52" s="10"/>
+        <v>24</v>
+      </c>
+      <c r="C52" s="10">
+        <v>0.27</v>
+      </c>
       <c r="D52" s="3">
         <v>1</v>
       </c>
@@ -3007,11 +3086,17 @@
         <v>0</v>
       </c>
       <c r="H52" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I52" s="10"/>
-      <c r="J52" s="10"/>
-      <c r="K52" s="10"/>
+        <v>9</v>
+      </c>
+      <c r="I52" s="10">
+        <v>0.78</v>
+      </c>
+      <c r="J52" s="10">
+        <v>0.92</v>
+      </c>
+      <c r="K52" s="10">
+        <v>0.09</v>
+      </c>
       <c r="L52" s="1">
         <v>0.33</v>
       </c>
@@ -3021,33 +3106,67 @@
       <c r="N52" s="9">
         <v>0</v>
       </c>
-      <c r="O52" s="10"/>
+      <c r="O52" s="10">
+        <v>0.98</v>
+      </c>
     </row>
     <row r="53" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
-      <c r="A53" s="5"/>
-      <c r="B53" s="5"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="5"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="7"/>
-      <c r="H53" s="7"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="5"/>
-      <c r="K53" s="6"/>
-      <c r="L53" s="7"/>
-      <c r="M53" s="7"/>
-      <c r="N53" s="7"/>
-      <c r="O53" s="7"/>
+      <c r="A53" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="B53" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C53" s="10">
+        <v>-0.05</v>
+      </c>
+      <c r="D53" s="3">
+        <v>1</v>
+      </c>
+      <c r="E53" s="3">
+        <v>25</v>
+      </c>
+      <c r="F53" s="3">
+        <v>1</v>
+      </c>
+      <c r="G53" s="1">
+        <v>0</v>
+      </c>
+      <c r="H53" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I53" s="10">
+        <v>-0.1</v>
+      </c>
+      <c r="J53" s="10">
+        <v>0.27</v>
+      </c>
+      <c r="K53" s="10">
+        <v>0.04</v>
+      </c>
+      <c r="L53" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="M53" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="N53" s="10">
+        <v>0.87</v>
+      </c>
+      <c r="O53" s="9">
+        <v>0.01</v>
+      </c>
     </row>
     <row r="54" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A54" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B54" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C54" s="10"/>
+        <v>36</v>
+      </c>
+      <c r="B54" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C54" s="10">
+        <v>0.62</v>
+      </c>
       <c r="D54" s="3">
         <v>1</v>
       </c>
@@ -3061,16 +3180,16 @@
         <v>0</v>
       </c>
       <c r="H54" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I54" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J54" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="K54" s="10" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="I54" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="J54" s="10">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="K54" s="10">
+        <v>0.26</v>
       </c>
       <c r="L54" s="1">
         <v>0.33</v>
@@ -3078,21 +3197,23 @@
       <c r="M54" s="1">
         <v>0.33</v>
       </c>
-      <c r="N54" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="O54" s="10" t="s">
-        <v>9</v>
+      <c r="N54" s="10">
+        <v>0.95</v>
+      </c>
+      <c r="O54" s="9">
+        <v>0.01</v>
       </c>
     </row>
     <row r="55" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A55" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B55" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C55" s="10"/>
+        <v>36</v>
+      </c>
+      <c r="B55" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C55" s="10">
+        <v>0.4</v>
+      </c>
       <c r="D55" s="3">
         <v>1</v>
       </c>
@@ -3106,16 +3227,16 @@
         <v>0</v>
       </c>
       <c r="H55" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I55" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J55" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="K55" s="10" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="I55" s="10">
+        <v>0.43</v>
+      </c>
+      <c r="J55" s="10">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="K55" s="10">
+        <v>0.33</v>
       </c>
       <c r="L55" s="1">
         <v>0.33</v>
@@ -3123,21 +3244,23 @@
       <c r="M55" s="1">
         <v>0.33</v>
       </c>
-      <c r="N55" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="O55" s="10" t="s">
-        <v>9</v>
+      <c r="N55" s="10">
+        <v>0.96</v>
+      </c>
+      <c r="O55" s="9">
+        <v>0.01</v>
       </c>
     </row>
     <row r="56" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A56" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="B56" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C56" s="10"/>
+        <v>37</v>
+      </c>
+      <c r="B56" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C56" s="10">
+        <v>0.17</v>
+      </c>
       <c r="D56" s="3">
         <v>1</v>
       </c>
@@ -3145,22 +3268,22 @@
         <v>25</v>
       </c>
       <c r="F56" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G56" s="1">
         <v>0</v>
       </c>
       <c r="H56" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I56" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J56" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="K56" s="10" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="I56" s="10">
+        <v>0.08</v>
+      </c>
+      <c r="J56" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="K56" s="10">
+        <v>0.02</v>
       </c>
       <c r="L56" s="1">
         <v>0.33</v>
@@ -3168,22 +3291,22 @@
       <c r="M56" s="1">
         <v>0.33</v>
       </c>
-      <c r="N56" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="O56" s="10" t="s">
-        <v>9</v>
+      <c r="N56" s="10">
+        <v>0.62</v>
+      </c>
+      <c r="O56" s="9">
+        <v>0.01</v>
       </c>
     </row>
     <row r="57" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A57" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B57" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="C57" s="10" t="s">
-        <v>22</v>
+        <v>37</v>
+      </c>
+      <c r="B57" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C57" s="14" t="s">
+        <v>29</v>
       </c>
       <c r="D57" s="3">
         <v>1</v>
@@ -3192,22 +3315,22 @@
         <v>25</v>
       </c>
       <c r="F57" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" s="1">
         <v>0</v>
       </c>
       <c r="H57" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I57" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J57" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="K57" s="10" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="I57" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="J57" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="K57" s="14" t="s">
+        <v>29</v>
       </c>
       <c r="L57" s="1">
         <v>0.33</v>
@@ -3215,22 +3338,22 @@
       <c r="M57" s="1">
         <v>0.33</v>
       </c>
-      <c r="N57" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="O57" s="10" t="s">
-        <v>9</v>
+      <c r="N57" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="O57" s="9">
+        <v>0.01</v>
       </c>
     </row>
     <row r="58" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A58" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B58" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C58" s="10" t="s">
-        <v>22</v>
+        <v>37</v>
+      </c>
+      <c r="B58" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C58" s="10">
+        <v>0.28000000000000003</v>
       </c>
       <c r="D58" s="3">
         <v>1</v>
@@ -3239,22 +3362,22 @@
         <v>25</v>
       </c>
       <c r="F58" s="3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G58" s="1">
         <v>0</v>
       </c>
       <c r="H58" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I58" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J58" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="K58" s="10" t="s">
-        <v>9</v>
+        <v>9</v>
+      </c>
+      <c r="I58" s="10">
+        <v>0.19</v>
+      </c>
+      <c r="J58" s="10">
+        <v>0.27</v>
+      </c>
+      <c r="K58" s="10">
+        <v>-0.13</v>
       </c>
       <c r="L58" s="1">
         <v>0.33</v>
@@ -3262,69 +3385,39 @@
       <c r="M58" s="1">
         <v>0.33</v>
       </c>
-      <c r="N58" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="O58" s="10" t="s">
-        <v>9</v>
+      <c r="N58" s="10">
+        <v>0.94</v>
+      </c>
+      <c r="O58" s="9">
+        <v>0.01</v>
       </c>
     </row>
     <row r="59" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
-      <c r="A59" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="B59" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="C59" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="D59" s="3">
-        <v>1</v>
-      </c>
-      <c r="E59" s="3">
-        <v>25</v>
-      </c>
-      <c r="F59" s="3">
-        <v>1</v>
-      </c>
-      <c r="G59" s="1">
-        <v>0</v>
-      </c>
-      <c r="H59" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="I59" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="J59" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="K59" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="L59" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="M59" s="1">
-        <v>0.33</v>
-      </c>
-      <c r="N59" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="O59" s="10" t="s">
-        <v>9</v>
-      </c>
+      <c r="A59" s="5"/>
+      <c r="B59" s="5"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="6"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="6"/>
+      <c r="G59" s="7"/>
+      <c r="H59" s="7"/>
+      <c r="I59" s="6"/>
+      <c r="J59" s="5"/>
+      <c r="K59" s="6"/>
+      <c r="L59" s="7"/>
+      <c r="M59" s="7"/>
+      <c r="N59" s="7"/>
+      <c r="O59" s="7"/>
     </row>
     <row r="60" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
       <c r="A60" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B60" s="11" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="C60" s="10">
-        <v>0.15</v>
+        <v>0.01</v>
       </c>
       <c r="D60" s="3">
         <v>1</v>
@@ -3333,22 +3426,22 @@
         <v>25</v>
       </c>
       <c r="F60" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60" s="1">
         <v>0</v>
       </c>
       <c r="H60" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I60" s="10">
-        <v>0</v>
+        <v>0.21</v>
       </c>
       <c r="J60" s="10">
-        <v>-0.13</v>
+        <v>0.22</v>
       </c>
       <c r="K60" s="10">
-        <v>0.23</v>
+        <v>0.04</v>
       </c>
       <c r="L60" s="1">
         <v>0.33</v>
@@ -3357,10 +3450,10 @@
         <v>0.33</v>
       </c>
       <c r="N60" s="10">
-        <v>0.92</v>
+        <v>0.57999999999999996</v>
       </c>
       <c r="O60" s="10">
-        <v>0.44</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="61" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
@@ -3368,10 +3461,10 @@
         <v>19</v>
       </c>
       <c r="B61" s="12" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C61" s="10">
-        <v>0.59</v>
+        <v>0.41</v>
       </c>
       <c r="D61" s="3">
         <v>1</v>
@@ -3380,22 +3473,22 @@
         <v>25</v>
       </c>
       <c r="F61" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G61" s="1">
         <v>0</v>
       </c>
       <c r="H61" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I61" s="10">
-        <v>0.83</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J61" s="10">
-        <v>0.94</v>
+        <v>0.56000000000000005</v>
       </c>
       <c r="K61" s="10">
-        <v>0.7</v>
+        <v>0.27</v>
       </c>
       <c r="L61" s="1">
         <v>0.33</v>
@@ -3404,10 +3497,10 @@
         <v>0.33</v>
       </c>
       <c r="N61" s="10">
-        <v>0.94</v>
+        <v>0.87</v>
       </c>
       <c r="O61" s="10">
-        <v>0.83</v>
+        <v>0.98</v>
       </c>
     </row>
     <row r="62" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
@@ -3415,10 +3508,10 @@
         <v>19</v>
       </c>
       <c r="B62" s="13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="C62" s="10">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="D62" s="3">
         <v>1</v>
@@ -3427,22 +3520,22 @@
         <v>25</v>
       </c>
       <c r="F62" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G62" s="1">
         <v>0</v>
       </c>
       <c r="H62" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I62" s="10">
-        <v>0.76</v>
+        <v>0.13</v>
       </c>
       <c r="J62" s="10">
-        <v>0.96</v>
+        <v>0.27</v>
       </c>
       <c r="K62" s="10">
-        <v>-0.15</v>
+        <v>0.04</v>
       </c>
       <c r="L62" s="1">
         <v>0.33</v>
@@ -3451,16 +3544,394 @@
         <v>0.33</v>
       </c>
       <c r="N62" s="10">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="O62" s="10">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="63" spans="1:15" ht="14.4" thickTop="1"/>
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="63" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
+      <c r="A63" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C63" s="10">
+        <v>0.02</v>
+      </c>
+      <c r="D63" s="3">
+        <v>1</v>
+      </c>
+      <c r="E63" s="3">
+        <v>25</v>
+      </c>
+      <c r="F63" s="3">
+        <v>0</v>
+      </c>
+      <c r="G63" s="1">
+        <v>0</v>
+      </c>
+      <c r="H63" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I63" s="10">
+        <v>0.25</v>
+      </c>
+      <c r="J63" s="10">
+        <v>0.24</v>
+      </c>
+      <c r="K63" s="10">
+        <v>0.05</v>
+      </c>
+      <c r="L63" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="M63" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="N63" s="10">
+        <v>0.54</v>
+      </c>
+      <c r="O63" s="10">
+        <v>0.03</v>
+      </c>
+    </row>
+    <row r="64" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
+      <c r="A64" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B64" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C64" s="10">
+        <v>0.01</v>
+      </c>
+      <c r="D64" s="3">
+        <v>1</v>
+      </c>
+      <c r="E64" s="3">
+        <v>25</v>
+      </c>
+      <c r="F64" s="3">
+        <v>0</v>
+      </c>
+      <c r="G64" s="1">
+        <v>0</v>
+      </c>
+      <c r="H64" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I64" s="10">
+        <v>0.47</v>
+      </c>
+      <c r="J64" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="K64" s="10">
+        <v>0.19</v>
+      </c>
+      <c r="L64" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="M64" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="N64" s="10">
+        <v>0.86</v>
+      </c>
+      <c r="O64" s="10">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="65" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
+      <c r="A65" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B65" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" s="10">
+        <v>-0.02</v>
+      </c>
+      <c r="D65" s="3">
+        <v>1</v>
+      </c>
+      <c r="E65" s="3">
+        <v>25</v>
+      </c>
+      <c r="F65" s="3">
+        <v>0</v>
+      </c>
+      <c r="G65" s="1">
+        <v>0</v>
+      </c>
+      <c r="H65" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I65" s="10">
+        <v>0.43</v>
+      </c>
+      <c r="J65" s="10">
+        <v>0.31</v>
+      </c>
+      <c r="K65" s="10">
+        <v>-0.08</v>
+      </c>
+      <c r="L65" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="M65" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="N65" s="10">
+        <v>0.8</v>
+      </c>
+      <c r="O65" s="10">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="66" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
+      <c r="A66" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B66" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C66" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D66" s="3">
+        <v>1</v>
+      </c>
+      <c r="E66" s="3">
+        <v>25</v>
+      </c>
+      <c r="F66" s="3">
+        <v>1</v>
+      </c>
+      <c r="G66" s="1">
+        <v>0</v>
+      </c>
+      <c r="H66" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I66" s="10">
+        <v>0.21</v>
+      </c>
+      <c r="J66" s="10">
+        <v>0.06</v>
+      </c>
+      <c r="K66" s="10">
+        <v>-0.02</v>
+      </c>
+      <c r="L66" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="M66" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="N66" s="10">
+        <v>0.7</v>
+      </c>
+      <c r="O66" s="10">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="67" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
+      <c r="A67" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B67" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C67" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="D67" s="3">
+        <v>1</v>
+      </c>
+      <c r="E67" s="3">
+        <v>25</v>
+      </c>
+      <c r="F67" s="3">
+        <v>1</v>
+      </c>
+      <c r="G67" s="1">
+        <v>0</v>
+      </c>
+      <c r="H67" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I67" s="10">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="J67" s="10">
+        <v>0.4</v>
+      </c>
+      <c r="K67" s="10">
+        <v>0.34</v>
+      </c>
+      <c r="L67" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="M67" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="N67" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="O67" s="10">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="68" spans="1:15" ht="16.8" thickTop="1" thickBot="1">
+      <c r="A68" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B68" s="13" t="s">
+        <v>24</v>
+      </c>
+      <c r="C68" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D68" s="3">
+        <v>1</v>
+      </c>
+      <c r="E68" s="3">
+        <v>25</v>
+      </c>
+      <c r="F68" s="3">
+        <v>1</v>
+      </c>
+      <c r="G68" s="1">
+        <v>0</v>
+      </c>
+      <c r="H68" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="I68" s="10">
+        <v>0.15</v>
+      </c>
+      <c r="J68" s="10">
+        <v>0.19</v>
+      </c>
+      <c r="K68" s="10">
+        <v>0.12</v>
+      </c>
+      <c r="L68" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="M68" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="N68" s="10">
+        <v>0.92</v>
+      </c>
+      <c r="O68" s="10">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="69" spans="1:15" ht="14.4" thickTop="1"/>
   </sheetData>
-  <phoneticPr fontId="7" type="noConversion"/>
-  <conditionalFormatting sqref="C3">
+  <phoneticPr fontId="8" type="noConversion"/>
+  <conditionalFormatting sqref="C8:C19">
+    <cfRule type="colorScale" priority="40">
+      <colorScale>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.9"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C28">
+    <cfRule type="colorScale" priority="24">
+      <colorScale>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.9"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C34:C45">
+    <cfRule type="colorScale" priority="22">
+      <colorScale>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.9"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C47:C56 C58">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.9"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C57">
+    <cfRule type="colorScale" priority="3">
+      <colorScale>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.9"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="C60:C68 C3 I62:K68 N62:O68">
+    <cfRule type="colorScale" priority="25">
+      <colorScale>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.9"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I11:I19">
+    <cfRule type="colorScale" priority="38">
+      <colorScale>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.9"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I24:I26 C2 K24:K27 K29 I5:I7 I14:I19 C21:C27 I30:I32 J27 I21:J23 C4:C7 C29:C32 J29:J32">
+    <cfRule type="colorScale" priority="43">
+      <colorScale>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.9"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I34:I39">
     <cfRule type="colorScale" priority="21">
       <colorScale>
         <cfvo type="num" val="0.1"/>
@@ -3472,8 +3943,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C8:C19">
-    <cfRule type="colorScale" priority="36">
+  <conditionalFormatting sqref="I43:I45">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="num" val="0.1"/>
         <cfvo type="num" val="0.5"/>
@@ -3484,7 +3955,115 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C28">
+  <conditionalFormatting sqref="I47:I56 I58">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.9"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I57:K57">
+    <cfRule type="colorScale" priority="2">
+      <colorScale>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.9"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I60:K60">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.9"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="I61:K61">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.9"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J34:J36">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.9"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J40:J45">
+    <cfRule type="colorScale" priority="19">
+      <colorScale>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.9"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J47:J56 J58">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.9"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="J28:K28">
+    <cfRule type="colorScale" priority="23">
+      <colorScale>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.9"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K21:K23">
+    <cfRule type="colorScale" priority="31">
+      <colorScale>
+        <cfvo type="num" val="0.1"/>
+        <cfvo type="num" val="0.5"/>
+        <cfvo type="num" val="0.9"/>
+        <color rgb="FFFF0000"/>
+        <color rgb="FFFFFF00"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="K34:K42">
     <cfRule type="colorScale" priority="20">
       <colorScale>
         <cfvo type="num" val="0.1"/>
@@ -3496,8 +4075,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I11:I19">
-    <cfRule type="colorScale" priority="34">
+  <conditionalFormatting sqref="K47:K56 K58">
+    <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="num" val="0.1"/>
         <cfvo type="num" val="0.5"/>
@@ -3508,8 +4087,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I24:I26 C2 K24:K27 K29 I5:I7 I14:I19 C21:C27 I30:I32 J27 I21:J23 C4:C7 C29:C32 J29:J32">
-    <cfRule type="colorScale" priority="39">
+  <conditionalFormatting sqref="N53:N56 N58">
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="num" val="0.1"/>
         <cfvo type="num" val="0.5"/>
@@ -3520,8 +4099,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J28:K28">
-    <cfRule type="colorScale" priority="19">
+  <conditionalFormatting sqref="N57">
+    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0.1"/>
         <cfvo type="num" val="0.5"/>
@@ -3532,8 +4111,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K21:K23">
-    <cfRule type="colorScale" priority="27">
+  <conditionalFormatting sqref="N60:O60">
+    <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="num" val="0.1"/>
         <cfvo type="num" val="0.5"/>
@@ -3544,79 +4123,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C34:C45">
-    <cfRule type="colorScale" priority="18">
-      <colorScale>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="0.9"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I34:I39">
-    <cfRule type="colorScale" priority="17">
-      <colorScale>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="0.9"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K34:K42">
-    <cfRule type="colorScale" priority="16">
-      <colorScale>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="0.9"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J40:J45">
-    <cfRule type="colorScale" priority="15">
-      <colorScale>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="0.9"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I43:I45">
-    <cfRule type="colorScale" priority="14">
-      <colorScale>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="0.9"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J34:J36">
-    <cfRule type="colorScale" priority="13">
-      <colorScale>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="0.9"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C54:C62">
+  <conditionalFormatting sqref="N61:O61">
     <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="num" val="0.1"/>
@@ -3628,128 +4135,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I56:K62">
-    <cfRule type="colorScale" priority="11">
-      <colorScale>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="0.9"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N56:O62">
-    <cfRule type="colorScale" priority="10">
-      <colorScale>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="0.9"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I55:K55">
-    <cfRule type="colorScale" priority="9">
-      <colorScale>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="0.9"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N55:O55">
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="0.9"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I54:K54">
-    <cfRule type="colorScale" priority="7">
-      <colorScale>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="0.9"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="N54:O54">
-    <cfRule type="colorScale" priority="6">
-      <colorScale>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="0.9"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="C47:C52">
+  <conditionalFormatting sqref="O47:O52">
     <cfRule type="colorScale" priority="5">
-      <colorScale>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="0.9"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="I47:I52">
-    <cfRule type="colorScale" priority="4">
-      <colorScale>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="0.9"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="K47:K52">
-    <cfRule type="colorScale" priority="3">
-      <colorScale>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="0.9"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="J47:J52">
-    <cfRule type="colorScale" priority="2">
-      <colorScale>
-        <cfvo type="num" val="0.1"/>
-        <cfvo type="num" val="0.5"/>
-        <cfvo type="num" val="0.9"/>
-        <color rgb="FFFF0000"/>
-        <color rgb="FFFFFF00"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="O47:O52">
-    <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="num" val="0.1"/>
         <cfvo type="num" val="0.5"/>
